--- a/consent_forms/034_social_media_post_sharing_consent_form--consent_forms.xlsx
+++ b/consent_forms/034_social_media_post_sharing_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>consent_form</t>
+          <t>share_on_facebook</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>consent_form</t>
+          <t>Share on Facebook</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>share_on_twitter</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Share on Twitter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>share_on_instagram</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Share on Instagram</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>share_on_linkedin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>Share on LinkedIn</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>share_on_facebook</t>
+          <t>share_on_youtube</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>share_on_facebook</t>
+          <t>Share on YouTube</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>share_on_twitter</t>
+          <t>share_on_tiktok</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>share_on_twitter</t>
+          <t>Share on TikTok</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>share_on_instagram</t>
+          <t>share_on_snapchat</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>share_on_instagram</t>
+          <t>Share on Snapchat</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>share_on_linkedin</t>
+          <t>share_on_whatsapp</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>share_on_linkedin</t>
+          <t>Share on WhatsApp</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>share_on_youtube</t>
+          <t>share_on_twitch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>share_on_youtube</t>
+          <t>Share on Twitch</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>share_on_pinterest</t>
+          <t>share_on_discord</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>share_on_pinterest</t>
+          <t>Share on Discord</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>share_on_tiktok</t>
+          <t>share_on_telegram</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>share_on_tiktok</t>
+          <t>Share on Telegram</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>share_on_snapchat</t>
+          <t>share_on_twitch_live</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>share_on_snapchat</t>
+          <t>Share on Twitch Live</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>share_on_whatsapp</t>
+          <t>share_on_vimeo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>share_on_whatsapp</t>
+          <t>Share on Vimeo</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>share_on_twitch</t>
+          <t>share_on_reddit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>share_on_twitch</t>
+          <t>Share on Reddit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>share_on_twitter_thread</t>
+          <t>share_on_pinterest</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>share_on_twitter_thread</t>
+          <t>Share on Pinterest</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>share_on_vimeo</t>
+          <t>share_on_twitch_channel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>share_on_vimeo</t>
+          <t>Share on Twitch Channel</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>share_on_discord</t>
+          <t>share_on_discord_server</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>share_on_discord</t>
+          <t>Share on Discord Server</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>share_on_telegram</t>
+          <t>share_on_facebook_live</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>share_on_telegram</t>
+          <t>Share on Facebook Live</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>share_on_roblox</t>
+          <t>share_on_youtube_tour</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>share_on_roblox</t>
+          <t>Share on YouTube Tour</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>share_on_tiktok</t>
+          <t>share_on_twitch_tour</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>share_on_tiktok</t>
+          <t>Share on Twitch Tour</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>share_on_roblox</t>
+          <t>Share on Roblox</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>share_on_discord_server</t>
+          <t>share_on_whatsapp_business</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>share_on_discord_server</t>
+          <t>Share on WhatsApp Business</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,177 +1026,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>share_on_youtube_tour</t>
+          <t>share_on_youtube_live</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>share_on_youtube_tour</t>
+          <t>Share on YouTube Live</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>share_on_twitch_live</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>share_on_twitch_live</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>share_on_vimeo</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>share_on_vimeo</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>share_on_whatsapp</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>share_on_whatsapp</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>share_on_twitch_channel</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>share_on_twitch_channel</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>share_on_tiktok_live</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>share_on_tiktok_live</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>share_on_facebook</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>share_on_facebook</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>share_on_youtube_live</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>share_on_youtube_live</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1213,12 +1052,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1246,12 +1085,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1102,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1119,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1136,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1153,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1170,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1187,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1204,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1221,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1399,454 +1238,454 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>share_on_pinterest_choices</t>
+          <t>share_on_tiktok_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>share_on_pinterest_choices</t>
+          <t>share_on_tiktok_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>share_on_tiktok_choices</t>
+          <t>share_on_snapchat_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>share_on_tiktok_choices</t>
+          <t>share_on_snapchat_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>share_on_snapchat_choices</t>
+          <t>share_on_whatsapp_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>share_on_snapchat_choices</t>
+          <t>share_on_whatsapp_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>share_on_whatsapp_choices</t>
+          <t>share_on_twitch_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>share_on_whatsapp_choices</t>
+          <t>share_on_twitch_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>share_on_twitch_choices</t>
+          <t>share_on_discord_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>share_on_twitch_choices</t>
+          <t>share_on_discord_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>share_on_twitter_thread_choices</t>
+          <t>share_on_telegram_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>share_on_twitter_thread_choices</t>
+          <t>share_on_telegram_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>share_on_vimeo_choices</t>
+          <t>share_on_twitch_live_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>share_on_vimeo_choices</t>
+          <t>share_on_twitch_live_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>share_on_discord_choices</t>
+          <t>share_on_vimeo_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>share_on_discord_choices</t>
+          <t>share_on_vimeo_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>share_on_telegram_choices</t>
+          <t>share_on_reddit_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>share_on_telegram_choices</t>
+          <t>share_on_reddit_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>share_on_roblox_choices</t>
+          <t>share_on_pinterest_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>share_on_roblox_choices</t>
+          <t>share_on_pinterest_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>share_on_tiktok_choices</t>
+          <t>share_on_twitch_channel_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>share_on_tiktok_choices</t>
+          <t>share_on_twitch_channel_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>share_on_roblox_choices</t>
+          <t>share_on_discord_server_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>share_on_roblox_choices</t>
+          <t>share_on_discord_server_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>share_on_discord_server_choices</t>
+          <t>share_on_facebook_live_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>share_on_discord_server_choices</t>
+          <t>share_on_facebook_live_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1858,12 +1697,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1875,250 +1714,148 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>share_on_twitch_live_choices</t>
+          <t>share_on_twitch_tour_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>share_on_twitch_live_choices</t>
+          <t>share_on_twitch_tour_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>share_on_vimeo_choices</t>
+          <t>share_on_roblox_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>share_on_vimeo_choices</t>
+          <t>share_on_roblox_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>share_on_whatsapp_choices</t>
+          <t>share_on_whatsapp_business_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>share_on_whatsapp_choices</t>
+          <t>share_on_whatsapp_business_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>share_on_twitch_channel_choices</t>
+          <t>share_on_youtube_live_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>share_on_twitch_channel_choices</t>
+          <t>share_on_youtube_live_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>share_on_tiktok_live_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>{'value':_true,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>{'value': True, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>share_on_tiktok_live_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>{'value':_false,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>{'value': False, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>share_on_facebook_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>{'value':_true,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>{'value': True, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>share_on_facebook_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>{'value':_false,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>{'value': False, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>share_on_youtube_live_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>{'value':_true,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>{'value': True, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>share_on_youtube_live_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>{'value':_false,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
